--- a/ltp_prev.xlsx
+++ b/ltp_prev.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -458,16 +458,16 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>475</v>
+        <v>484.1</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>500.75</v>
+        <v>467.95</v>
       </c>
       <c r="D2" t="n">
-        <v>496</v>
+        <v>495.85</v>
       </c>
       <c r="E2" t="n">
-        <v>470.6</v>
+        <v>474.9</v>
       </c>
     </row>
     <row r="3">
@@ -477,16 +477,16 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>7253</v>
+        <v>6836</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>7219</v>
+        <v>6820</v>
       </c>
       <c r="D3" t="n">
-        <v>7340</v>
+        <v>6911</v>
       </c>
       <c r="E3" t="n">
-        <v>7121</v>
+        <v>6812</v>
       </c>
     </row>
     <row r="4">
@@ -496,16 +496,16 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>363.3</v>
+        <v>408.3</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>364.9</v>
+        <v>397.35</v>
       </c>
       <c r="D4" t="n">
-        <v>369.2</v>
+        <v>409</v>
       </c>
       <c r="E4" t="n">
-        <v>360.8</v>
+        <v>403</v>
       </c>
     </row>
     <row r="5">
@@ -515,16 +515,16 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>64.61</v>
+        <v>60.02</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>64.06</v>
+        <v>58.55</v>
       </c>
       <c r="D5" t="n">
-        <v>68.19</v>
+        <v>60.72</v>
       </c>
       <c r="E5" t="n">
-        <v>63.51</v>
+        <v>59.55</v>
       </c>
     </row>
     <row r="6">
@@ -534,16 +534,16 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>2937.4</v>
+        <v>3157.3</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>2973.1</v>
+        <v>3083.6</v>
       </c>
       <c r="D6" t="n">
-        <v>2995</v>
+        <v>3183</v>
       </c>
       <c r="E6" t="n">
-        <v>2926.8</v>
+        <v>3102.6</v>
       </c>
     </row>
     <row r="7">
@@ -553,16 +553,16 @@
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>1804.6</v>
+        <v>1828.1</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>1824.5</v>
+        <v>1800.1</v>
       </c>
       <c r="D7" t="n">
-        <v>1819.8</v>
+        <v>1852.9</v>
       </c>
       <c r="E7" t="n">
-        <v>1796.4</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="8">
@@ -572,16 +572,16 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>1055.5</v>
+        <v>1160.1</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>1070.3</v>
+        <v>1142.9</v>
       </c>
       <c r="D8" t="n">
-        <v>1099.1</v>
+        <v>1164.6</v>
       </c>
       <c r="E8" t="n">
-        <v>1049</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="9">
@@ -591,16 +591,16 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>5498</v>
+        <v>5669.5</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>5451.5</v>
+        <v>5648.5</v>
       </c>
       <c r="D9" t="n">
-        <v>5757</v>
+        <v>5727.5</v>
       </c>
       <c r="E9" t="n">
-        <v>5472</v>
+        <v>5635</v>
       </c>
     </row>
     <row r="10">
@@ -610,16 +610,16 @@
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>447.85</v>
+        <v>436.45</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>459.75</v>
+        <v>428.15</v>
       </c>
       <c r="D10" t="n">
-        <v>461.5</v>
+        <v>440.8</v>
       </c>
       <c r="E10" t="n">
-        <v>445.45</v>
+        <v>434.15</v>
       </c>
     </row>
     <row r="11">
@@ -629,16 +629,16 @@
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>8176.5</v>
+        <v>8841</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>8272.5</v>
+        <v>8845.5</v>
       </c>
       <c r="D11" t="n">
-        <v>8325</v>
+        <v>8850</v>
       </c>
       <c r="E11" t="n">
-        <v>8146</v>
+        <v>8773.5</v>
       </c>
     </row>
     <row r="12">
@@ -648,16 +648,16 @@
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>394.5</v>
+        <v>440.1</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>399.75</v>
+        <v>439.65</v>
       </c>
       <c r="D12" t="n">
-        <v>403.35</v>
+        <v>445.5</v>
       </c>
       <c r="E12" t="n">
-        <v>392</v>
+        <v>438.1</v>
       </c>
     </row>
     <row r="13">
@@ -667,16 +667,16 @@
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>155.44</v>
+        <v>157.49</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>163.62</v>
+        <v>155.19</v>
       </c>
       <c r="D13" t="n">
-        <v>162.8</v>
+        <v>157.69</v>
       </c>
       <c r="E13" t="n">
-        <v>154.86</v>
+        <v>155.91</v>
       </c>
     </row>
     <row r="14">
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>1578.2</v>
+        <v>1333.8</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>1598.6</v>
+        <v>1317.1</v>
       </c>
       <c r="D14" t="n">
-        <v>1614.8</v>
+        <v>1337.9</v>
       </c>
       <c r="E14" t="n">
-        <v>1568.2</v>
+        <v>1316.1</v>
       </c>
     </row>
     <row r="15">
@@ -705,16 +705,16 @@
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>6855.5</v>
+        <v>6236</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>7002.5</v>
+        <v>6183</v>
       </c>
       <c r="D15" t="n">
-        <v>6950</v>
+        <v>6325</v>
       </c>
       <c r="E15" t="n">
-        <v>6758.5</v>
+        <v>6170.5</v>
       </c>
     </row>
     <row r="16">
@@ -724,16 +724,16 @@
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>984.7</v>
+        <v>1072.1</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>1005</v>
+        <v>1047.4</v>
       </c>
       <c r="D16" t="n">
-        <v>1012</v>
+        <v>1079.9</v>
       </c>
       <c r="E16" t="n">
-        <v>971.1</v>
+        <v>1062.9</v>
       </c>
     </row>
     <row r="17">
@@ -743,16 +743,16 @@
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>1426.4</v>
+        <v>1564.7</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>1435.9</v>
+        <v>1587.4</v>
       </c>
       <c r="D17" t="n">
-        <v>1453.4</v>
+        <v>1575.7</v>
       </c>
       <c r="E17" t="n">
-        <v>1411</v>
+        <v>1544.3</v>
       </c>
     </row>
     <row r="18">
@@ -762,16 +762,16 @@
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>10460</v>
+        <v>10156</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>10808.5</v>
+        <v>10155</v>
       </c>
       <c r="D18" t="n">
-        <v>10750</v>
+        <v>10298</v>
       </c>
       <c r="E18" t="n">
-        <v>10388.5</v>
+        <v>10115</v>
       </c>
     </row>
     <row r="19">
@@ -781,16 +781,16 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>1783.6</v>
+        <v>1916</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>1809.1</v>
+        <v>1895</v>
       </c>
       <c r="D19" t="n">
-        <v>1813</v>
+        <v>1920.5</v>
       </c>
       <c r="E19" t="n">
-        <v>1776.9</v>
+        <v>1893.4</v>
       </c>
     </row>
     <row r="20">
@@ -800,16 +800,16 @@
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>908.25</v>
+        <v>1020.5</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>931.15</v>
+        <v>1003.8</v>
       </c>
       <c r="D20" t="n">
-        <v>937.8</v>
+        <v>1023.9</v>
       </c>
       <c r="E20" t="n">
-        <v>895.3</v>
+        <v>1004.2</v>
       </c>
     </row>
     <row r="21">
@@ -819,16 +819,16 @@
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>2205.5</v>
+        <v>2252.9</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>2194.7</v>
+        <v>2201.8</v>
       </c>
       <c r="D21" t="n">
-        <v>2351.5</v>
+        <v>2275</v>
       </c>
       <c r="E21" t="n">
-        <v>2166</v>
+        <v>2230.4</v>
       </c>
     </row>
     <row r="22">
@@ -838,16 +838,16 @@
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>514.8</v>
+        <v>566.9</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>530.2</v>
+        <v>567.45</v>
       </c>
       <c r="D22" t="n">
-        <v>530.1</v>
+        <v>569.15</v>
       </c>
       <c r="E22" t="n">
-        <v>510.15</v>
+        <v>562.6</v>
       </c>
     </row>
     <row r="23">
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>208.3</v>
+        <v>210</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>205.83</v>
+        <v>199.86</v>
       </c>
       <c r="D23" t="n">
-        <v>212.48</v>
+        <v>211.8</v>
       </c>
       <c r="E23" t="n">
-        <v>207.42</v>
+        <v>205</v>
       </c>
     </row>
     <row r="24">
@@ -876,16 +876,16 @@
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>268.5</v>
+        <v>250.95</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>270.95</v>
+        <v>244.6</v>
       </c>
       <c r="D24" t="n">
-        <v>273.4</v>
+        <v>254.35</v>
       </c>
       <c r="E24" t="n">
-        <v>267.15</v>
+        <v>246.3</v>
       </c>
     </row>
     <row r="25">
@@ -895,16 +895,16 @@
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>668.95</v>
+        <v>690.7</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>692.6</v>
+        <v>672.3</v>
       </c>
       <c r="D25" t="n">
-        <v>675.95</v>
+        <v>709.9</v>
       </c>
       <c r="E25" t="n">
-        <v>661.35</v>
+        <v>682.6</v>
       </c>
     </row>
     <row r="26">
@@ -914,16 +914,16 @@
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>410.75</v>
+        <v>414.85</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>419.1</v>
+        <v>406.2</v>
       </c>
       <c r="D26" t="n">
-        <v>417.25</v>
+        <v>415.45</v>
       </c>
       <c r="E26" t="n">
-        <v>409.9</v>
+        <v>408.9</v>
       </c>
     </row>
     <row r="27">
@@ -933,16 +933,16 @@
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>1957.2</v>
+        <v>2117</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>1938.6</v>
+        <v>2130.6</v>
       </c>
       <c r="D27" t="n">
-        <v>1967.8</v>
+        <v>2146.6</v>
       </c>
       <c r="E27" t="n">
-        <v>1920</v>
+        <v>2108.1</v>
       </c>
     </row>
     <row r="28">
@@ -952,16 +952,16 @@
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>416.75</v>
+        <v>395.25</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>422.35</v>
+        <v>381.6</v>
       </c>
       <c r="D28" t="n">
-        <v>424.25</v>
+        <v>395.8</v>
       </c>
       <c r="E28" t="n">
-        <v>413.05</v>
+        <v>388.75</v>
       </c>
     </row>
     <row r="29">
@@ -971,16 +971,16 @@
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>428.65</v>
+        <v>418.5</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>432.2</v>
+        <v>403.55</v>
       </c>
       <c r="D29" t="n">
-        <v>439.65</v>
+        <v>419.8</v>
       </c>
       <c r="E29" t="n">
-        <v>425.65</v>
+        <v>404.85</v>
       </c>
     </row>
     <row r="30">
@@ -990,16 +990,16 @@
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>5204.5</v>
+        <v>5353</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>5335.5</v>
+        <v>5361.5</v>
       </c>
       <c r="D30" t="n">
-        <v>5310</v>
+        <v>5405</v>
       </c>
       <c r="E30" t="n">
-        <v>5164.5</v>
+        <v>5323</v>
       </c>
     </row>
     <row r="31">
@@ -1009,16 +1009,16 @@
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>4146.1</v>
+        <v>3811.6</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>4248.4</v>
+        <v>3805.7</v>
       </c>
       <c r="D31" t="n">
-        <v>4224.9</v>
+        <v>3840</v>
       </c>
       <c r="E31" t="n">
-        <v>4127.9</v>
+        <v>3760.1</v>
       </c>
     </row>
     <row r="32">
@@ -1028,16 +1028,16 @@
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>319.35</v>
+        <v>290.15</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>328.1</v>
+        <v>274.85</v>
       </c>
       <c r="D32" t="n">
-        <v>332</v>
+        <v>293</v>
       </c>
       <c r="E32" t="n">
-        <v>316.5</v>
+        <v>281.65</v>
       </c>
     </row>
     <row r="33">
@@ -1047,16 +1047,16 @@
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>130.8</v>
+        <v>128.78</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>134.16</v>
+        <v>124.8</v>
       </c>
       <c r="D33" t="n">
-        <v>134.8</v>
+        <v>131.48</v>
       </c>
       <c r="E33" t="n">
-        <v>130.15</v>
+        <v>125.75</v>
       </c>
     </row>
     <row r="34">
@@ -1066,16 +1066,16 @@
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>829.65</v>
+        <v>921.5</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>832.95</v>
+        <v>916.1</v>
       </c>
       <c r="D34" t="n">
-        <v>838</v>
+        <v>931.9</v>
       </c>
       <c r="E34" t="n">
-        <v>821.5</v>
+        <v>915.5</v>
       </c>
     </row>
     <row r="35">
@@ -1085,16 +1085,16 @@
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>466.4</v>
+        <v>453.75</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>478.15</v>
+        <v>453.85</v>
       </c>
       <c r="D35" t="n">
-        <v>480.5</v>
+        <v>456.65</v>
       </c>
       <c r="E35" t="n">
-        <v>463</v>
+        <v>453</v>
       </c>
     </row>
     <row r="36">
@@ -1104,16 +1104,16 @@
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>1537.7</v>
+        <v>1807.8</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>1579.2</v>
+        <v>1791.9</v>
       </c>
       <c r="D36" t="n">
-        <v>1588.4</v>
+        <v>1827</v>
       </c>
       <c r="E36" t="n">
-        <v>1530.2</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="37">
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>1401</v>
+        <v>1439.4</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>1418.2</v>
+        <v>1441.3</v>
       </c>
       <c r="D37" t="n">
-        <v>1429.2</v>
+        <v>1454.5</v>
       </c>
       <c r="E37" t="n">
-        <v>1382.7</v>
+        <v>1436.1</v>
       </c>
     </row>
     <row r="38">
@@ -1142,16 +1142,16 @@
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>457.9</v>
+        <v>429.3</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>463.05</v>
+        <v>429.9</v>
       </c>
       <c r="D38" t="n">
-        <v>474</v>
+        <v>432.6</v>
       </c>
       <c r="E38" t="n">
-        <v>455.9</v>
+        <v>426.75</v>
       </c>
     </row>
     <row r="39">
@@ -1161,16 +1161,16 @@
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>1421.8</v>
+        <v>1503.8</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>1388.4</v>
+        <v>1468.6</v>
       </c>
       <c r="D39" t="n">
-        <v>1449.8</v>
+        <v>1513.8</v>
       </c>
       <c r="E39" t="n">
-        <v>1410.6</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="40">
@@ -1180,16 +1180,16 @@
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>463.65</v>
+        <v>463.75</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>472.3</v>
+        <v>457.1</v>
       </c>
       <c r="D40" t="n">
-        <v>477.65</v>
+        <v>470.55</v>
       </c>
       <c r="E40" t="n">
-        <v>460.15</v>
+        <v>463</v>
       </c>
     </row>
     <row r="41">
@@ -1199,16 +1199,16 @@
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>1753.6</v>
+        <v>2067.8</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>1831.7</v>
+        <v>2014.3</v>
       </c>
       <c r="D41" t="n">
-        <v>1848.9</v>
+        <v>2079.7</v>
       </c>
       <c r="E41" t="n">
-        <v>1720.2</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="42">
@@ -1218,16 +1218,16 @@
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>281.15</v>
+        <v>261.7</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>288.25</v>
+        <v>259</v>
       </c>
       <c r="D42" t="n">
-        <v>292.6</v>
+        <v>264.55</v>
       </c>
       <c r="E42" t="n">
-        <v>272.3</v>
+        <v>261.15</v>
       </c>
     </row>
     <row r="43">
@@ -1237,16 +1237,16 @@
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>5881</v>
+        <v>5621.5</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>6027.5</v>
+        <v>5542.5</v>
       </c>
       <c r="D43" t="n">
-        <v>6063.5</v>
+        <v>5714</v>
       </c>
       <c r="E43" t="n">
-        <v>5855.5</v>
+        <v>5607</v>
       </c>
     </row>
     <row r="44">
@@ -1256,16 +1256,16 @@
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>443.4</v>
+        <v>443.5</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>445.45</v>
+        <v>443.15</v>
       </c>
       <c r="D44" t="n">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="E44" t="n">
-        <v>440.1</v>
+        <v>441.05</v>
       </c>
     </row>
     <row r="45">
@@ -1275,16 +1275,16 @@
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>1748.2</v>
+        <v>1786.5</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>1792.1</v>
+        <v>1742.3</v>
       </c>
       <c r="D45" t="n">
-        <v>1800.2</v>
+        <v>1795.2</v>
       </c>
       <c r="E45" t="n">
-        <v>1739</v>
+        <v>1765.1</v>
       </c>
     </row>
     <row r="46">
@@ -1294,16 +1294,16 @@
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>1410.1</v>
+        <v>1526.2</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>1448.3</v>
+        <v>1546.2</v>
       </c>
       <c r="D46" t="n">
-        <v>1457.9</v>
+        <v>1564.6</v>
       </c>
       <c r="E46" t="n">
-        <v>1400.2</v>
+        <v>1522.2</v>
       </c>
     </row>
     <row r="47">
@@ -1313,16 +1313,16 @@
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>1682</v>
+        <v>1644</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>1714.8</v>
+        <v>1621.2</v>
       </c>
       <c r="D47" t="n">
-        <v>1718.5</v>
+        <v>1669.3</v>
       </c>
       <c r="E47" t="n">
-        <v>1656.3</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="48">
@@ -1332,16 +1332,16 @@
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>69.59999999999999</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>81.05</v>
+        <v>64.81</v>
       </c>
       <c r="D48" t="n">
-        <v>76</v>
+        <v>65.5</v>
       </c>
       <c r="E48" t="n">
-        <v>66.55</v>
+        <v>64.59999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -1351,16 +1351,16 @@
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>6667</v>
+        <v>6836</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>6797.5</v>
+        <v>6813</v>
       </c>
       <c r="D49" t="n">
-        <v>6784.5</v>
+        <v>6862.5</v>
       </c>
       <c r="E49" t="n">
-        <v>6590</v>
+        <v>6778</v>
       </c>
     </row>
     <row r="50">
@@ -1370,16 +1370,16 @@
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>11524</v>
+        <v>13421</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>11756</v>
+        <v>13477</v>
       </c>
       <c r="D50" t="n">
-        <v>11760</v>
+        <v>13973</v>
       </c>
       <c r="E50" t="n">
-        <v>11480</v>
+        <v>13362</v>
       </c>
     </row>
     <row r="51">
@@ -1389,16 +1389,16 @@
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>590.6</v>
+        <v>685.75</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>593.9</v>
+        <v>659.6</v>
       </c>
       <c r="D51" t="n">
-        <v>607.9</v>
+        <v>692</v>
       </c>
       <c r="E51" t="n">
-        <v>586.55</v>
+        <v>666.95</v>
       </c>
     </row>
     <row r="52">
@@ -1408,16 +1408,16 @@
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>1303.5</v>
+        <v>1244.3</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>1319</v>
+        <v>1269.5</v>
       </c>
       <c r="D52" t="n">
-        <v>1322.7</v>
+        <v>1251.8</v>
       </c>
       <c r="E52" t="n">
-        <v>1297.5</v>
+        <v>1232.5</v>
       </c>
     </row>
     <row r="53">
@@ -1427,16 +1427,16 @@
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>7177</v>
+        <v>7365.5</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>7419</v>
+        <v>7361</v>
       </c>
       <c r="D53" t="n">
-        <v>7364.5</v>
+        <v>7455</v>
       </c>
       <c r="E53" t="n">
-        <v>7131.5</v>
+        <v>7335</v>
       </c>
     </row>
     <row r="54">
@@ -1446,16 +1446,16 @@
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>2859.8</v>
+        <v>2941.8</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>2880.4</v>
+        <v>2908.6</v>
       </c>
       <c r="D54" t="n">
-        <v>2913</v>
+        <v>2969</v>
       </c>
       <c r="E54" t="n">
-        <v>2750</v>
+        <v>2919</v>
       </c>
     </row>
     <row r="55">
@@ -1465,16 +1465,16 @@
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>250.58</v>
+        <v>289.65</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>256.51</v>
+        <v>292.45</v>
       </c>
       <c r="D55" t="n">
-        <v>257.1</v>
+        <v>293.4</v>
       </c>
       <c r="E55" t="n">
-        <v>249.41</v>
+        <v>287.15</v>
       </c>
     </row>
     <row r="56">
@@ -1484,16 +1484,16 @@
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>386.5</v>
+        <v>424.4</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>394.15</v>
+        <v>425.2</v>
       </c>
       <c r="D56" t="n">
-        <v>395.95</v>
+        <v>431</v>
       </c>
       <c r="E56" t="n">
-        <v>384.75</v>
+        <v>422.15</v>
       </c>
     </row>
     <row r="57">
@@ -1503,16 +1503,16 @@
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>288.95</v>
+        <v>329.85</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>288.9</v>
+        <v>327.75</v>
       </c>
       <c r="D57" t="n">
-        <v>293.9</v>
+        <v>331.7</v>
       </c>
       <c r="E57" t="n">
-        <v>283.6</v>
+        <v>327.85</v>
       </c>
     </row>
     <row r="58">
@@ -1522,16 +1522,16 @@
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>2274.9</v>
+        <v>2282.9</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>2384.9</v>
+        <v>2267.2</v>
       </c>
       <c r="D58" t="n">
-        <v>2390.2</v>
+        <v>2304.1</v>
       </c>
       <c r="E58" t="n">
-        <v>2257.8</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="59">
@@ -1541,16 +1541,16 @@
         </is>
       </c>
       <c r="B59" s="1" t="n">
-        <v>504.3</v>
+        <v>502.45</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>516.15</v>
+        <v>504.6</v>
       </c>
       <c r="D59" t="n">
-        <v>521</v>
+        <v>511</v>
       </c>
       <c r="E59" t="n">
-        <v>502</v>
+        <v>500.65</v>
       </c>
     </row>
     <row r="60">
@@ -1560,16 +1560,16 @@
         </is>
       </c>
       <c r="B60" s="1" t="n">
-        <v>1029.3</v>
+        <v>1088.4</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>1044.4</v>
+        <v>1087.4</v>
       </c>
       <c r="D60" t="n">
-        <v>1047</v>
+        <v>1099.4</v>
       </c>
       <c r="E60" t="n">
-        <v>1024.1</v>
+        <v>1084.3</v>
       </c>
     </row>
     <row r="61">
@@ -1579,16 +1579,16 @@
         </is>
       </c>
       <c r="B61" s="1" t="n">
-        <v>1762.7</v>
+        <v>2133</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>1788.6</v>
+        <v>2029.9</v>
       </c>
       <c r="D61" t="n">
-        <v>1833.1</v>
+        <v>2138</v>
       </c>
       <c r="E61" t="n">
-        <v>1750</v>
+        <v>2040.8</v>
       </c>
     </row>
     <row r="62">
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>773.85</v>
+        <v>889.85</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>782.6</v>
+        <v>882.05</v>
       </c>
       <c r="D62" t="n">
-        <v>800</v>
+        <v>901.8</v>
       </c>
       <c r="E62" t="n">
-        <v>768.55</v>
+        <v>883.6</v>
       </c>
     </row>
     <row r="63">
@@ -1617,16 +1617,16 @@
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>3122.4</v>
+        <v>3213.6</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>3170</v>
+        <v>3191.9</v>
       </c>
       <c r="D63" t="n">
-        <v>3184</v>
+        <v>3246</v>
       </c>
       <c r="E63" t="n">
-        <v>3111.4</v>
+        <v>3208</v>
       </c>
     </row>
     <row r="64">
@@ -1636,16 +1636,16 @@
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>401.15</v>
+        <v>289.7</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>369.8</v>
+        <v>286.45</v>
       </c>
       <c r="D64" t="n">
-        <v>410</v>
+        <v>351.15</v>
       </c>
       <c r="E64" t="n">
-        <v>375.5</v>
+        <v>332.3</v>
       </c>
     </row>
     <row r="65">
@@ -1655,16 +1655,16 @@
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>4303.8</v>
+        <v>4506.8</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>4413</v>
+        <v>4378.9</v>
       </c>
       <c r="D65" t="n">
-        <v>4408.6</v>
+        <v>4524.9</v>
       </c>
       <c r="E65" t="n">
-        <v>4255.3</v>
+        <v>4402.8</v>
       </c>
     </row>
     <row r="66">
@@ -1673,17 +1673,17 @@
           <t>HAVELLS</t>
         </is>
       </c>
-      <c r="B66" s="1" t="n">
-        <v>1176.8</v>
+      <c r="B66" t="n">
+        <v>1188.4</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>1211</v>
+        <v>1190.8</v>
       </c>
       <c r="D66" t="n">
-        <v>1210</v>
+        <v>1206.1</v>
       </c>
       <c r="E66" t="n">
-        <v>1166</v>
+        <v>1179.9</v>
       </c>
     </row>
     <row r="67">
@@ -1693,16 +1693,16 @@
         </is>
       </c>
       <c r="B67" s="1" t="n">
-        <v>1183.8</v>
+        <v>1164.1</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>1165.2</v>
+        <v>1150.4</v>
       </c>
       <c r="D67" t="n">
-        <v>1191.7</v>
+        <v>1178.7</v>
       </c>
       <c r="E67" t="n">
-        <v>1177</v>
+        <v>1153.5</v>
       </c>
     </row>
     <row r="68">
@@ -1712,16 +1712,16 @@
         </is>
       </c>
       <c r="B68" s="1" t="n">
-        <v>2674.3</v>
+        <v>2761.2</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>2716.3</v>
+        <v>2737.1</v>
       </c>
       <c r="D68" t="n">
-        <v>2768.4</v>
+        <v>2789.8</v>
       </c>
       <c r="E68" t="n">
-        <v>2652.6</v>
+        <v>2748</v>
       </c>
     </row>
     <row r="69">
@@ -1731,16 +1731,16 @@
         </is>
       </c>
       <c r="B69" s="1" t="n">
-        <v>744.55</v>
+        <v>824.95</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>758.65</v>
+        <v>817.55</v>
       </c>
       <c r="D69" t="n">
-        <v>760.5</v>
+        <v>827.7</v>
       </c>
       <c r="E69" t="n">
-        <v>737.75</v>
+        <v>822</v>
       </c>
     </row>
     <row r="70">
@@ -1750,16 +1750,16 @@
         </is>
       </c>
       <c r="B70" s="1" t="n">
-        <v>594.8</v>
+        <v>567.7</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>609.6</v>
+        <v>551.85</v>
       </c>
       <c r="D70" t="n">
-        <v>611.8</v>
+        <v>570</v>
       </c>
       <c r="E70" t="n">
-        <v>588.8</v>
+        <v>556.7</v>
       </c>
     </row>
     <row r="71">
@@ -1769,16 +1769,16 @@
         </is>
       </c>
       <c r="B71" s="1" t="n">
-        <v>4903</v>
+        <v>4949.1</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>5075</v>
+        <v>4898.5</v>
       </c>
       <c r="D71" t="n">
-        <v>5134.5</v>
+        <v>4968</v>
       </c>
       <c r="E71" t="n">
-        <v>4875.5</v>
+        <v>4900</v>
       </c>
     </row>
     <row r="72">
@@ -1788,16 +1788,16 @@
         </is>
       </c>
       <c r="B72" s="1" t="n">
-        <v>1126.7</v>
+        <v>967.45</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>1149.7</v>
+        <v>963.45</v>
       </c>
       <c r="D72" t="n">
-        <v>1157</v>
+        <v>985.6</v>
       </c>
       <c r="E72" t="n">
-        <v>1122</v>
+        <v>964.7</v>
       </c>
     </row>
     <row r="73">
@@ -1807,16 +1807,16 @@
         </is>
       </c>
       <c r="B73" s="1" t="n">
-        <v>538.7</v>
+        <v>498.65</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>555.35</v>
+        <v>486.45</v>
       </c>
       <c r="D73" t="n">
-        <v>564.65</v>
+        <v>511.8</v>
       </c>
       <c r="E73" t="n">
-        <v>528</v>
+        <v>497.25</v>
       </c>
     </row>
     <row r="74">
@@ -1826,16 +1826,16 @@
         </is>
       </c>
       <c r="B74" s="1" t="n">
-        <v>1256.4</v>
+        <v>1401.2</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>1272.7</v>
+        <v>1380.7</v>
       </c>
       <c r="D74" t="n">
-        <v>1285.9</v>
+        <v>1408.2</v>
       </c>
       <c r="E74" t="n">
-        <v>1247.9</v>
+        <v>1398.4</v>
       </c>
     </row>
     <row r="75">
@@ -1845,16 +1845,16 @@
         </is>
       </c>
       <c r="B75" s="1" t="n">
-        <v>1792.2</v>
+        <v>1826.2</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>1850.6</v>
+        <v>1794.7</v>
       </c>
       <c r="D75" t="n">
-        <v>1849</v>
+        <v>1837.4</v>
       </c>
       <c r="E75" t="n">
-        <v>1739.5</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="76">
@@ -1864,16 +1864,16 @@
         </is>
       </c>
       <c r="B76" s="1" t="n">
-        <v>503.95</v>
+        <v>510.35</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>522.9</v>
+        <v>490.7</v>
       </c>
       <c r="D76" t="n">
-        <v>520.4</v>
+        <v>515.5</v>
       </c>
       <c r="E76" t="n">
-        <v>498.25</v>
+        <v>496.6</v>
       </c>
     </row>
     <row r="77">
@@ -1883,16 +1883,16 @@
         </is>
       </c>
       <c r="B77" s="1" t="n">
-        <v>128.31</v>
+        <v>119.64</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>126.59</v>
+        <v>117.85</v>
       </c>
       <c r="D77" t="n">
-        <v>129.8</v>
+        <v>120.65</v>
       </c>
       <c r="E77" t="n">
-        <v>126.43</v>
+        <v>118.44</v>
       </c>
     </row>
     <row r="78">
@@ -1902,16 +1902,16 @@
         </is>
       </c>
       <c r="B78" s="1" t="n">
-        <v>160.47</v>
+        <v>154.06</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>164.61</v>
+        <v>151.77</v>
       </c>
       <c r="D78" t="n">
-        <v>165.6</v>
+        <v>154.7</v>
       </c>
       <c r="E78" t="n">
-        <v>158.31</v>
+        <v>151.4</v>
       </c>
     </row>
     <row r="79">
@@ -1921,16 +1921,16 @@
         </is>
       </c>
       <c r="B79" s="1" t="n">
-        <v>654.25</v>
+        <v>752.3</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>667.7</v>
+        <v>731.45</v>
       </c>
       <c r="D79" t="n">
-        <v>671</v>
+        <v>754</v>
       </c>
       <c r="E79" t="n">
-        <v>650.6</v>
+        <v>734.45</v>
       </c>
     </row>
     <row r="80">
@@ -1940,16 +1940,16 @@
         </is>
       </c>
       <c r="B80" s="1" t="n">
-        <v>381.95</v>
+        <v>380.5</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>400.6</v>
+        <v>372.05</v>
       </c>
       <c r="D80" t="n">
-        <v>402.95</v>
+        <v>383.5</v>
       </c>
       <c r="E80" t="n">
-        <v>376.1</v>
+        <v>377.35</v>
       </c>
     </row>
     <row r="81">
@@ -1959,16 +1959,16 @@
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>2015.7</v>
+        <v>1924</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>2020.1</v>
+        <v>1924.7</v>
       </c>
       <c r="D81" t="n">
-        <v>2028.6</v>
+        <v>1936.6</v>
       </c>
       <c r="E81" t="n">
-        <v>1966.4</v>
+        <v>1906.2</v>
       </c>
     </row>
     <row r="82">
@@ -1978,16 +1978,16 @@
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>4405</v>
+        <v>5312</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>4570</v>
+        <v>5229.5</v>
       </c>
       <c r="D82" t="n">
-        <v>4552.5</v>
+        <v>5363</v>
       </c>
       <c r="E82" t="n">
-        <v>4381.2</v>
+        <v>5285.5</v>
       </c>
     </row>
     <row r="83">
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="B83" s="1" t="n">
-        <v>914.35</v>
+        <v>1015.8</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>932.3</v>
+        <v>1015.15</v>
       </c>
       <c r="D83" t="n">
-        <v>935.5</v>
+        <v>1031.65</v>
       </c>
       <c r="E83" t="n">
-        <v>910.35</v>
+        <v>1013.7</v>
       </c>
     </row>
     <row r="84">
@@ -2016,16 +2016,16 @@
         </is>
       </c>
       <c r="B84" s="1" t="n">
-        <v>442.05</v>
+        <v>406.15</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>436.25</v>
+        <v>398.15</v>
       </c>
       <c r="D84" t="n">
-        <v>449.4</v>
+        <v>407.85</v>
       </c>
       <c r="E84" t="n">
-        <v>432.1</v>
+        <v>395.05</v>
       </c>
     </row>
     <row r="85">
@@ -2035,16 +2035,16 @@
         </is>
       </c>
       <c r="B85" s="1" t="n">
-        <v>1160.9</v>
+        <v>1068</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>1159.9</v>
+        <v>1050.8</v>
       </c>
       <c r="D85" t="n">
-        <v>1210</v>
+        <v>1077.2</v>
       </c>
       <c r="E85" t="n">
-        <v>1153.6</v>
+        <v>1064.7</v>
       </c>
     </row>
     <row r="86">
@@ -2054,16 +2054,16 @@
         </is>
       </c>
       <c r="B86" s="1" t="n">
-        <v>716.85</v>
+        <v>758.75</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>710.1</v>
+        <v>743.25</v>
       </c>
       <c r="D86" t="n">
-        <v>746.6</v>
+        <v>763.2</v>
       </c>
       <c r="E86" t="n">
-        <v>707.4</v>
+        <v>749.2</v>
       </c>
     </row>
     <row r="87">
@@ -2073,16 +2073,16 @@
         </is>
       </c>
       <c r="B87" s="1" t="n">
-        <v>1524.4</v>
+        <v>1787.9</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>1572.4</v>
+        <v>1770.4</v>
       </c>
       <c r="D87" t="n">
-        <v>1618.7</v>
+        <v>1799.4</v>
       </c>
       <c r="E87" t="n">
-        <v>1482.9</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="88">
@@ -2092,16 +2092,16 @@
         </is>
       </c>
       <c r="B88" s="1" t="n">
-        <v>1207.2</v>
+        <v>1051.3</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>1220.6</v>
+        <v>1029.8</v>
       </c>
       <c r="D88" t="n">
-        <v>1228.7</v>
+        <v>1063.6</v>
       </c>
       <c r="E88" t="n">
-        <v>1191.7</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="89">
@@ -2111,16 +2111,16 @@
         </is>
       </c>
       <c r="B89" s="1" t="n">
-        <v>238.95</v>
+        <v>241.96</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>242.89</v>
+        <v>233.37</v>
       </c>
       <c r="D89" t="n">
-        <v>244.41</v>
+        <v>243.5</v>
       </c>
       <c r="E89" t="n">
-        <v>238.05</v>
+        <v>236.13</v>
       </c>
     </row>
     <row r="90">
@@ -2130,16 +2130,16 @@
         </is>
       </c>
       <c r="B90" s="1" t="n">
-        <v>5171</v>
+        <v>5398.5</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>5301</v>
+        <v>5393.5</v>
       </c>
       <c r="D90" t="n">
-        <v>5296.5</v>
+        <v>5487.5</v>
       </c>
       <c r="E90" t="n">
-        <v>5125</v>
+        <v>5380.5</v>
       </c>
     </row>
     <row r="91">
@@ -2149,16 +2149,16 @@
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>1278</v>
+        <v>1245.4</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>1309.3</v>
+        <v>1225.8</v>
       </c>
       <c r="D91" t="n">
-        <v>1307.9</v>
+        <v>1259</v>
       </c>
       <c r="E91" t="n">
-        <v>1270.3</v>
+        <v>1241.6</v>
       </c>
     </row>
     <row r="92">
@@ -2168,16 +2168,16 @@
         </is>
       </c>
       <c r="B92" s="1" t="n">
-        <v>427.5</v>
+        <v>438.05</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>427.3</v>
+        <v>429.35</v>
       </c>
       <c r="D92" t="n">
-        <v>437.75</v>
+        <v>440.9</v>
       </c>
       <c r="E92" t="n">
-        <v>422.15</v>
+        <v>435.95</v>
       </c>
     </row>
     <row r="93">
@@ -2187,16 +2187,16 @@
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>384.2</v>
+        <v>377.6</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>388.7</v>
+        <v>377.15</v>
       </c>
       <c r="D93" t="n">
-        <v>392.55</v>
+        <v>381.15</v>
       </c>
       <c r="E93" t="n">
-        <v>381.25</v>
+        <v>376.9</v>
       </c>
     </row>
     <row r="94">
@@ -2206,16 +2206,16 @@
         </is>
       </c>
       <c r="B94" s="1" t="n">
-        <v>1607.4</v>
+        <v>1692.8</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>1617.2</v>
+        <v>1684.6</v>
       </c>
       <c r="D94" t="n">
-        <v>1622.4</v>
+        <v>1703</v>
       </c>
       <c r="E94" t="n">
-        <v>1585.9</v>
+        <v>1680.1</v>
       </c>
     </row>
     <row r="95">
@@ -2225,16 +2225,16 @@
         </is>
       </c>
       <c r="B95" s="1" t="n">
-        <v>1362</v>
+        <v>1537.8</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>1381.7</v>
+        <v>1507.4</v>
       </c>
       <c r="D95" t="n">
-        <v>1392.3</v>
+        <v>1548</v>
       </c>
       <c r="E95" t="n">
-        <v>1356.4</v>
+        <v>1507.3</v>
       </c>
     </row>
     <row r="96">
@@ -2244,16 +2244,16 @@
         </is>
       </c>
       <c r="B96" s="1" t="n">
-        <v>533.15</v>
+        <v>549.15</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>556.45</v>
+        <v>539.8</v>
       </c>
       <c r="D96" t="n">
-        <v>561.45</v>
+        <v>553.7</v>
       </c>
       <c r="E96" t="n">
-        <v>531.05</v>
+        <v>546.7</v>
       </c>
     </row>
     <row r="97">
@@ -2263,16 +2263,16 @@
         </is>
       </c>
       <c r="B97" s="1" t="n">
-        <v>286.6</v>
+        <v>321.25</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>281.7</v>
+        <v>321.1</v>
       </c>
       <c r="D97" t="n">
-        <v>289.4</v>
+        <v>328.75</v>
       </c>
       <c r="E97" t="n">
-        <v>281.1</v>
+        <v>319</v>
       </c>
     </row>
     <row r="98">
@@ -2282,16 +2282,16 @@
         </is>
       </c>
       <c r="B98" s="1" t="n">
-        <v>4061.6</v>
+        <v>4037.2</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>3988.6</v>
+        <v>3854.4</v>
       </c>
       <c r="D98" t="n">
-        <v>4149.4</v>
+        <v>4083.2</v>
       </c>
       <c r="E98" t="n">
-        <v>4011.6</v>
+        <v>3900</v>
       </c>
       <c r="K98" s="1" t="n"/>
       <c r="L98" s="1" t="n"/>
@@ -2303,16 +2303,16 @@
         </is>
       </c>
       <c r="B99" s="1" t="n">
-        <v>3432.4</v>
+        <v>3278.2</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>3491.6</v>
+        <v>3217.6</v>
       </c>
       <c r="D99" t="n">
-        <v>3596.6</v>
+        <v>3284</v>
       </c>
       <c r="E99" t="n">
-        <v>3390.7</v>
+        <v>3233</v>
       </c>
     </row>
     <row r="100">
@@ -2322,16 +2322,16 @@
         </is>
       </c>
       <c r="B100" s="1" t="n">
-        <v>2267.7</v>
+        <v>2496.3</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>2276.4</v>
+        <v>2503.3</v>
       </c>
       <c r="D100" t="n">
-        <v>2297.5</v>
+        <v>2521.8</v>
       </c>
       <c r="E100" t="n">
-        <v>2256.2</v>
+        <v>2482</v>
       </c>
     </row>
     <row r="101">
@@ -2341,16 +2341,16 @@
         </is>
       </c>
       <c r="B101" s="1" t="n">
-        <v>3045.6</v>
+        <v>3129.4</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>3121.6</v>
+        <v>3085.4</v>
       </c>
       <c r="D101" t="n">
-        <v>3130.5</v>
+        <v>3135</v>
       </c>
       <c r="E101" t="n">
-        <v>3005.1</v>
+        <v>3110.5</v>
       </c>
     </row>
     <row r="102">
@@ -2360,16 +2360,16 @@
         </is>
       </c>
       <c r="B102" s="1" t="n">
-        <v>303.65</v>
+        <v>340.85</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>305.2</v>
+        <v>336.75</v>
       </c>
       <c r="D102" t="n">
-        <v>309.45</v>
+        <v>347</v>
       </c>
       <c r="E102" t="n">
-        <v>300.9</v>
+        <v>339.6</v>
       </c>
     </row>
     <row r="103">
@@ -2379,16 +2379,16 @@
         </is>
       </c>
       <c r="B103" s="1" t="n">
-        <v>325.4</v>
+        <v>341.3</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>328.75</v>
+        <v>332.45</v>
       </c>
       <c r="D103" t="n">
-        <v>331.8</v>
+        <v>342.95</v>
       </c>
       <c r="E103" t="n">
-        <v>323.5</v>
+        <v>337.2</v>
       </c>
     </row>
     <row r="104">
@@ -2398,16 +2398,16 @@
         </is>
       </c>
       <c r="B104" s="1" t="n">
-        <v>821.7</v>
+        <v>852.5</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>833.8</v>
+        <v>860.05</v>
       </c>
       <c r="D104" t="n">
-        <v>838</v>
+        <v>858.55</v>
       </c>
       <c r="E104" t="n">
-        <v>817.1</v>
+        <v>847.3</v>
       </c>
     </row>
     <row r="105">
@@ -2417,16 +2417,16 @@
         </is>
       </c>
       <c r="B105" s="1" t="n">
-        <v>2954.5</v>
+        <v>2770.7</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>3158.5</v>
+        <v>2785.4</v>
       </c>
       <c r="D105" t="n">
-        <v>3101.8</v>
+        <v>2791.9</v>
       </c>
       <c r="E105" t="n">
-        <v>2906.2</v>
+        <v>2745.3</v>
       </c>
     </row>
     <row r="106">
@@ -2436,16 +2436,16 @@
         </is>
       </c>
       <c r="B106" s="1" t="n">
-        <v>555.35</v>
+        <v>567.95</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>536.15</v>
+        <v>560.05</v>
       </c>
       <c r="D106" t="n">
-        <v>565</v>
+        <v>570.95</v>
       </c>
       <c r="E106" t="n">
-        <v>536.3</v>
+        <v>557.5</v>
       </c>
     </row>
     <row r="107">
@@ -2455,16 +2455,16 @@
         </is>
       </c>
       <c r="B107" s="1" t="n">
-        <v>1674</v>
+        <v>1633.1</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>1682.3</v>
+        <v>1576.8</v>
       </c>
       <c r="D107" t="n">
-        <v>1688</v>
+        <v>1638.1</v>
       </c>
       <c r="E107" t="n">
-        <v>1653.6</v>
+        <v>1586.8</v>
       </c>
     </row>
     <row r="108">
@@ -2474,16 +2474,16 @@
         </is>
       </c>
       <c r="B108" s="1" t="n">
-        <v>1095</v>
+        <v>1126.3</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>1103.2</v>
+        <v>1122.7</v>
       </c>
       <c r="D108" t="n">
-        <v>1121</v>
+        <v>1130.6</v>
       </c>
       <c r="E108" t="n">
-        <v>1074</v>
+        <v>1120.3</v>
       </c>
     </row>
     <row r="109">
@@ -2493,16 +2493,16 @@
         </is>
       </c>
       <c r="B109" s="1" t="n">
-        <v>2271.4</v>
+        <v>2321.9</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>2232.9</v>
+        <v>2261.3</v>
       </c>
       <c r="D109" t="n">
-        <v>2297</v>
+        <v>2345</v>
       </c>
       <c r="E109" t="n">
-        <v>2259.9</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="110">
@@ -2512,16 +2512,16 @@
         </is>
       </c>
       <c r="B110" s="1" t="n">
-        <v>3342.9</v>
+        <v>3129.4</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>3306.9</v>
+        <v>3057.4</v>
       </c>
       <c r="D110" t="n">
-        <v>3388.9</v>
+        <v>3147.8</v>
       </c>
       <c r="E110" t="n">
-        <v>3243</v>
+        <v>3111.2</v>
       </c>
     </row>
     <row r="111">
@@ -2531,16 +2531,16 @@
         </is>
       </c>
       <c r="B111" s="1" t="n">
-        <v>1100.2</v>
+        <v>1212.7</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>1088.9</v>
+        <v>1218.2</v>
       </c>
       <c r="D111" t="n">
-        <v>1122</v>
+        <v>1232.8</v>
       </c>
       <c r="E111" t="n">
-        <v>1083.8</v>
+        <v>1204.3</v>
       </c>
     </row>
     <row r="112">
@@ -2550,16 +2550,16 @@
         </is>
       </c>
       <c r="B112" s="1" t="n">
-        <v>995</v>
+        <v>1204.05</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>1005.65</v>
+        <v>1201.85</v>
       </c>
       <c r="D112" t="n">
-        <v>1026.45</v>
+        <v>1218.8</v>
       </c>
       <c r="E112" t="n">
-        <v>982.5</v>
+        <v>1201.1</v>
       </c>
     </row>
     <row r="113">
@@ -2569,16 +2569,16 @@
         </is>
       </c>
       <c r="B113" s="1" t="n">
-        <v>7129</v>
+        <v>7712</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>7244.5</v>
+        <v>7689</v>
       </c>
       <c r="D113" t="n">
-        <v>7360</v>
+        <v>7761</v>
       </c>
       <c r="E113" t="n">
-        <v>6970</v>
+        <v>7655</v>
       </c>
     </row>
     <row r="114">
@@ -2588,16 +2588,16 @@
         </is>
       </c>
       <c r="B114" s="1" t="n">
-        <v>87.98999999999999</v>
+        <v>84.92</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>92.28</v>
+        <v>84.42</v>
       </c>
       <c r="D114" t="n">
-        <v>92.38</v>
+        <v>86.05</v>
       </c>
       <c r="E114" t="n">
-        <v>87.39</v>
+        <v>84.75</v>
       </c>
     </row>
     <row r="115">
@@ -2607,16 +2607,16 @@
         </is>
       </c>
       <c r="B115" s="1" t="n">
-        <v>386.9</v>
+        <v>344.55</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>398.15</v>
+        <v>343.7</v>
       </c>
       <c r="D115" t="n">
-        <v>398.55</v>
+        <v>348.8</v>
       </c>
       <c r="E115" t="n">
-        <v>385.1</v>
+        <v>343.2</v>
       </c>
     </row>
     <row r="116">
@@ -2626,16 +2626,16 @@
         </is>
       </c>
       <c r="B116" s="1" t="n">
-        <v>1707.1</v>
+        <v>1924.8</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>1692.6</v>
+        <v>1873.2</v>
       </c>
       <c r="D116" t="n">
-        <v>1744</v>
+        <v>1934.1</v>
       </c>
       <c r="E116" t="n">
-        <v>1684.2</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="117">
@@ -2645,16 +2645,16 @@
         </is>
       </c>
       <c r="B117" s="1" t="n">
-        <v>265.4</v>
+        <v>244.96</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>274.05</v>
+        <v>243.65</v>
       </c>
       <c r="D117" t="n">
-        <v>272.05</v>
+        <v>245.39</v>
       </c>
       <c r="E117" t="n">
-        <v>261.55</v>
+        <v>243.72</v>
       </c>
     </row>
     <row r="118">
@@ -2664,16 +2664,16 @@
         </is>
       </c>
       <c r="B118" s="1" t="n">
-        <v>1118.8</v>
+        <v>1341.8</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>1128.2</v>
+        <v>1262.9</v>
       </c>
       <c r="D118" t="n">
-        <v>1141</v>
+        <v>1359</v>
       </c>
       <c r="E118" t="n">
-        <v>1112</v>
+        <v>1287.6</v>
       </c>
     </row>
     <row r="119">
@@ -2683,16 +2683,16 @@
         </is>
       </c>
       <c r="B119" s="1" t="n">
-        <v>5194.3</v>
+        <v>5053.9</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>5098.4</v>
+        <v>4829.9</v>
       </c>
       <c r="D119" t="n">
-        <v>5278</v>
+        <v>5065.4</v>
       </c>
       <c r="E119" t="n">
-        <v>5152.3</v>
+        <v>4903</v>
       </c>
     </row>
     <row r="120">
@@ -2702,16 +2702,16 @@
         </is>
       </c>
       <c r="B120" s="1" t="n">
-        <v>271.05</v>
+        <v>278.95</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>278.8</v>
+        <v>277.15</v>
       </c>
       <c r="D120" t="n">
-        <v>278.1</v>
+        <v>282.8</v>
       </c>
       <c r="E120" t="n">
-        <v>266.85</v>
+        <v>277.95</v>
       </c>
     </row>
     <row r="121">
@@ -2721,16 +2721,16 @@
         </is>
       </c>
       <c r="B121" s="1" t="n">
-        <v>1482.8</v>
+        <v>1598.5</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>1480.7</v>
+        <v>1590.4</v>
       </c>
       <c r="D121" t="n">
-        <v>1500.7</v>
+        <v>1613.8</v>
       </c>
       <c r="E121" t="n">
-        <v>1466.5</v>
+        <v>1585.8</v>
       </c>
     </row>
     <row r="122">
@@ -2740,16 +2740,16 @@
         </is>
       </c>
       <c r="B122" s="1" t="n">
-        <v>1926.8</v>
+        <v>2166.9</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>1985.9</v>
+        <v>2118.2</v>
       </c>
       <c r="D122" t="n">
-        <v>1981.8</v>
+        <v>2173.1</v>
       </c>
       <c r="E122" t="n">
-        <v>1913</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="123">
@@ -2759,16 +2759,16 @@
         </is>
       </c>
       <c r="B123" s="1" t="n">
-        <v>9477.5</v>
+        <v>9210.5</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>9664</v>
+        <v>9074</v>
       </c>
       <c r="D123" t="n">
-        <v>9747</v>
+        <v>9232</v>
       </c>
       <c r="E123" t="n">
-        <v>9426</v>
+        <v>9094</v>
       </c>
     </row>
     <row r="124">
@@ -2778,16 +2778,16 @@
         </is>
       </c>
       <c r="B124" s="1" t="n">
-        <v>290.55</v>
+        <v>283.1</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>300.15</v>
+        <v>281.35</v>
       </c>
       <c r="D124" t="n">
-        <v>300.65</v>
+        <v>283.8</v>
       </c>
       <c r="E124" t="n">
-        <v>285.45</v>
+        <v>281.35</v>
       </c>
     </row>
     <row r="125">
@@ -2797,16 +2797,16 @@
         </is>
       </c>
       <c r="B125" s="1" t="n">
-        <v>188.07</v>
+        <v>207.05</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>176.49</v>
+        <v>204.36</v>
       </c>
       <c r="D125" t="n">
-        <v>193.55</v>
+        <v>208.5</v>
       </c>
       <c r="E125" t="n">
-        <v>178.21</v>
+        <v>202.6</v>
       </c>
     </row>
     <row r="126">
@@ -2816,16 +2816,16 @@
         </is>
       </c>
       <c r="B126" s="1" t="n">
-        <v>871.2</v>
+        <v>942.1</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>886.8</v>
+        <v>922.1</v>
       </c>
       <c r="D126" t="n">
-        <v>888</v>
+        <v>945.95</v>
       </c>
       <c r="E126" t="n">
-        <v>866</v>
+        <v>927.2</v>
       </c>
     </row>
     <row r="127">
@@ -2835,16 +2835,16 @@
         </is>
       </c>
       <c r="B127" s="1" t="n">
-        <v>345</v>
+        <v>380.65</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>348.25</v>
+        <v>362.8</v>
       </c>
       <c r="D127" t="n">
-        <v>349.85</v>
+        <v>381.6</v>
       </c>
       <c r="E127" t="n">
-        <v>341.25</v>
+        <v>365.9</v>
       </c>
     </row>
     <row r="128">
@@ -2854,16 +2854,16 @@
         </is>
       </c>
       <c r="B128" s="1" t="n">
-        <v>337.65</v>
+        <v>351.95</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>339.7</v>
+        <v>352</v>
       </c>
       <c r="D128" t="n">
-        <v>342.4</v>
+        <v>356.65</v>
       </c>
       <c r="E128" t="n">
-        <v>335</v>
+        <v>350.75</v>
       </c>
     </row>
     <row r="129">
@@ -2873,16 +2873,16 @@
         </is>
       </c>
       <c r="B129" s="1" t="n">
-        <v>1321.2</v>
+        <v>1307.8</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>1350.5</v>
+        <v>1279.8</v>
       </c>
       <c r="D129" t="n">
-        <v>1353.4</v>
+        <v>1311.1</v>
       </c>
       <c r="E129" t="n">
-        <v>1317</v>
+        <v>1296.4</v>
       </c>
     </row>
     <row r="130">
@@ -2892,16 +2892,16 @@
         </is>
       </c>
       <c r="B130" s="1" t="n">
-        <v>624.4</v>
+        <v>611.65</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>625.25</v>
+        <v>588.2</v>
       </c>
       <c r="D130" t="n">
-        <v>632.2</v>
+        <v>614.5</v>
       </c>
       <c r="E130" t="n">
-        <v>617.15</v>
+        <v>596.35</v>
       </c>
     </row>
     <row r="131">
@@ -2911,16 +2911,16 @@
         </is>
       </c>
       <c r="B131" s="1" t="n">
-        <v>1830.1</v>
+        <v>1862.9</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>1864.5</v>
+        <v>1821.7</v>
       </c>
       <c r="D131" t="n">
-        <v>1856.3</v>
+        <v>1866</v>
       </c>
       <c r="E131" t="n">
-        <v>1820.5</v>
+        <v>1840.3</v>
       </c>
     </row>
     <row r="132">
@@ -2930,16 +2930,16 @@
         </is>
       </c>
       <c r="B132" s="1" t="n">
-        <v>964.4</v>
+        <v>1036</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>967.8</v>
+        <v>1022.1</v>
       </c>
       <c r="D132" t="n">
-        <v>972.4</v>
+        <v>1047.8</v>
       </c>
       <c r="E132" t="n">
-        <v>960.3</v>
+        <v>1023.5</v>
       </c>
     </row>
     <row r="133">
@@ -2949,16 +2949,16 @@
         </is>
       </c>
       <c r="B133" s="1" t="n">
-        <v>3844</v>
+        <v>3496.5</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>3878.7</v>
+        <v>3476.4</v>
       </c>
       <c r="D133" t="n">
-        <v>3937.3</v>
+        <v>3542</v>
       </c>
       <c r="E133" t="n">
-        <v>3744.6</v>
+        <v>3486</v>
       </c>
     </row>
     <row r="134">
@@ -2968,16 +2968,16 @@
         </is>
       </c>
       <c r="B134" s="1" t="n">
-        <v>2715.8</v>
+        <v>2774.6</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>2736.8</v>
+        <v>2756.9</v>
       </c>
       <c r="D134" t="n">
-        <v>2740.9</v>
+        <v>2799.9</v>
       </c>
       <c r="E134" t="n">
-        <v>2678.8</v>
+        <v>2765.3</v>
       </c>
     </row>
     <row r="135">
@@ -2987,16 +2987,16 @@
         </is>
       </c>
       <c r="B135" s="1" t="n">
-        <v>1111.8</v>
+        <v>1082.6</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>1154.4</v>
+        <v>1076</v>
       </c>
       <c r="D135" t="n">
-        <v>1159.1</v>
+        <v>1103</v>
       </c>
       <c r="E135" t="n">
-        <v>1089</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="136">
@@ -3006,16 +3006,16 @@
         </is>
       </c>
       <c r="B136" s="1" t="n">
-        <v>1799.2</v>
+        <v>1935.5</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>1844.3</v>
+        <v>1938.7</v>
       </c>
       <c r="D136" t="n">
-        <v>1846.7</v>
+        <v>1953.9</v>
       </c>
       <c r="E136" t="n">
-        <v>1785.3</v>
+        <v>1926.6</v>
       </c>
     </row>
     <row r="137">
@@ -3025,16 +3025,16 @@
         </is>
       </c>
       <c r="B137" s="1" t="n">
-        <v>502.15</v>
+        <v>499.7</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>512.9</v>
+        <v>499.25</v>
       </c>
       <c r="D137" t="n">
-        <v>518.4</v>
+        <v>506.35</v>
       </c>
       <c r="E137" t="n">
-        <v>498</v>
+        <v>498.15</v>
       </c>
     </row>
     <row r="138">
@@ -3044,16 +3044,16 @@
         </is>
       </c>
       <c r="B138" s="1" t="n">
-        <v>442</v>
+        <v>420.35</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>460.4</v>
+        <v>415.4</v>
       </c>
       <c r="D138" t="n">
-        <v>462.6</v>
+        <v>423.85</v>
       </c>
       <c r="E138" t="n">
-        <v>436.05</v>
+        <v>418.95</v>
       </c>
     </row>
     <row r="139">
@@ -3063,16 +3063,16 @@
         </is>
       </c>
       <c r="B139" s="1" t="n">
-        <v>758</v>
+        <v>721.05</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>774.55</v>
+        <v>713.7</v>
       </c>
       <c r="D139" t="n">
-        <v>774.55</v>
+        <v>729.9</v>
       </c>
       <c r="E139" t="n">
-        <v>755</v>
+        <v>718</v>
       </c>
     </row>
     <row r="140">
@@ -3082,16 +3082,16 @@
         </is>
       </c>
       <c r="B140" s="1" t="n">
-        <v>1965</v>
+        <v>1856.2</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>1966.6</v>
+        <v>1870.4</v>
       </c>
       <c r="D140" t="n">
-        <v>1984.5</v>
+        <v>1901.5</v>
       </c>
       <c r="E140" t="n">
-        <v>1907.4</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="141">
@@ -3101,16 +3101,16 @@
         </is>
       </c>
       <c r="B141" s="1" t="n">
-        <v>420.75</v>
+        <v>381.3</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>425.8</v>
+        <v>375.5</v>
       </c>
       <c r="D141" t="n">
-        <v>432.7</v>
+        <v>382.8</v>
       </c>
       <c r="E141" t="n">
-        <v>419.65</v>
+        <v>377.7</v>
       </c>
     </row>
     <row r="142">
@@ -3120,16 +3120,16 @@
         </is>
       </c>
       <c r="B142" s="1" t="n">
-        <v>208.02</v>
+        <v>191.19</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>214.7</v>
+        <v>187.91</v>
       </c>
       <c r="D142" t="n">
-        <v>215.41</v>
+        <v>193.3</v>
       </c>
       <c r="E142" t="n">
-        <v>206.7</v>
+        <v>190.04</v>
       </c>
     </row>
     <row r="143">
@@ -3139,16 +3139,16 @@
         </is>
       </c>
       <c r="B143" s="1" t="n">
-        <v>2258.9</v>
+        <v>2069</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>2284.2</v>
+        <v>2049.5</v>
       </c>
       <c r="D143" t="n">
-        <v>2334</v>
+        <v>2099.6</v>
       </c>
       <c r="E143" t="n">
-        <v>2235</v>
+        <v>2064.6</v>
       </c>
     </row>
     <row r="144">
@@ -3158,16 +3158,16 @@
         </is>
       </c>
       <c r="B144" s="1" t="n">
-        <v>1483.9</v>
+        <v>1454.8</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>1455.6</v>
+        <v>1426.3</v>
       </c>
       <c r="D144" t="n">
-        <v>1496.6</v>
+        <v>1466.3</v>
       </c>
       <c r="E144" t="n">
-        <v>1460.1</v>
+        <v>1445.3</v>
       </c>
     </row>
     <row r="145">
@@ -3177,16 +3177,16 @@
         </is>
       </c>
       <c r="B145" s="1" t="n">
-        <v>4074.9</v>
+        <v>4584.4</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>4137.9</v>
+        <v>4555.8</v>
       </c>
       <c r="D145" t="n">
-        <v>4157.8</v>
+        <v>4602.8</v>
       </c>
       <c r="E145" t="n">
-        <v>4059</v>
+        <v>4560.7</v>
       </c>
     </row>
     <row r="146">
@@ -3196,16 +3196,16 @@
         </is>
       </c>
       <c r="B146" s="1" t="n">
-        <v>393.9</v>
+        <v>337.95</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>400.95</v>
+        <v>331.5</v>
       </c>
       <c r="D146" t="n">
-        <v>407.5</v>
+        <v>340.25</v>
       </c>
       <c r="E146" t="n">
-        <v>390.7</v>
+        <v>333.75</v>
       </c>
     </row>
     <row r="147">
@@ -3215,16 +3215,16 @@
         </is>
       </c>
       <c r="B147" s="1" t="n">
-        <v>4410.8</v>
+        <v>4901.5</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>4537.8</v>
+        <v>4898.2</v>
       </c>
       <c r="D147" t="n">
-        <v>4537.8</v>
+        <v>4910</v>
       </c>
       <c r="E147" t="n">
-        <v>4356.1</v>
+        <v>4795.2</v>
       </c>
     </row>
     <row r="148">
@@ -3234,16 +3234,16 @@
         </is>
       </c>
       <c r="B148" s="1" t="n">
-        <v>1420.3</v>
+        <v>1419.4</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>1440.5</v>
+        <v>1414.9</v>
       </c>
       <c r="D148" t="n">
-        <v>1466.5</v>
+        <v>1452.9</v>
       </c>
       <c r="E148" t="n">
-        <v>1407</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="149">
@@ -3253,16 +3253,16 @@
         </is>
       </c>
       <c r="B149" s="1" t="n">
-        <v>4224</v>
+        <v>2902.8</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>4248.6</v>
+        <v>2904.1</v>
       </c>
       <c r="D149" t="n">
-        <v>4335.7</v>
+        <v>2931</v>
       </c>
       <c r="E149" t="n">
-        <v>4190</v>
+        <v>2896.8</v>
       </c>
     </row>
     <row r="150">
@@ -3272,16 +3272,16 @@
         </is>
       </c>
       <c r="B150" s="1" t="n">
-        <v>3355.7</v>
+        <v>3623.1</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>3384.6</v>
+        <v>3626.1</v>
       </c>
       <c r="D150" t="n">
-        <v>3456.9</v>
+        <v>3662.3</v>
       </c>
       <c r="E150" t="n">
-        <v>3315.2</v>
+        <v>3608.6</v>
       </c>
     </row>
     <row r="151">
@@ -3291,16 +3291,16 @@
         </is>
       </c>
       <c r="B151" s="1" t="n">
-        <v>1320</v>
+        <v>1329.3</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>1339.8</v>
+        <v>1328.2</v>
       </c>
       <c r="D151" t="n">
-        <v>1338.3</v>
+        <v>1341.9</v>
       </c>
       <c r="E151" t="n">
-        <v>1310</v>
+        <v>1325.9</v>
       </c>
     </row>
     <row r="152">
@@ -3310,16 +3310,16 @@
         </is>
       </c>
       <c r="B152" s="1" t="n">
-        <v>11482</v>
+        <v>11711</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>11689</v>
+        <v>11524</v>
       </c>
       <c r="D152" t="n">
-        <v>11779</v>
+        <v>11725</v>
       </c>
       <c r="E152" t="n">
-        <v>11338</v>
+        <v>11615</v>
       </c>
     </row>
     <row r="153">
@@ -3329,16 +3329,16 @@
         </is>
       </c>
       <c r="B153" s="1" t="n">
-        <v>644.8</v>
+        <v>594.75</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>656.15</v>
+        <v>581.85</v>
       </c>
       <c r="D153" t="n">
-        <v>660.9</v>
+        <v>599.8</v>
       </c>
       <c r="E153" t="n">
-        <v>638.5</v>
+        <v>592.5</v>
       </c>
     </row>
     <row r="154">
@@ -3348,16 +3348,16 @@
         </is>
       </c>
       <c r="B154" s="1" t="n">
-        <v>352.6</v>
+        <v>272.55</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>354.7</v>
+        <v>271.35</v>
       </c>
       <c r="D154" t="n">
-        <v>359.15</v>
+        <v>276.75</v>
       </c>
       <c r="E154" t="n">
-        <v>350</v>
+        <v>272.2</v>
       </c>
     </row>
     <row r="155">
@@ -3367,16 +3367,16 @@
         </is>
       </c>
       <c r="B155" s="1" t="n">
-        <v>1245.7</v>
+        <v>1286.7</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>1261.8</v>
+        <v>1269.4</v>
       </c>
       <c r="D155" t="n">
-        <v>1300</v>
+        <v>1290</v>
       </c>
       <c r="E155" t="n">
-        <v>1232.2</v>
+        <v>1272.3</v>
       </c>
     </row>
     <row r="156">
@@ -3386,16 +3386,16 @@
         </is>
       </c>
       <c r="B156" s="1" t="n">
-        <v>93.11</v>
+        <v>97.47</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>91.45999999999999</v>
+        <v>99.79000000000001</v>
       </c>
       <c r="D156" t="n">
-        <v>95.45999999999999</v>
+        <v>101.96</v>
       </c>
       <c r="E156" t="n">
-        <v>91.31</v>
+        <v>96.79000000000001</v>
       </c>
     </row>
     <row r="157">
@@ -3405,16 +3405,16 @@
         </is>
       </c>
       <c r="B157" s="1" t="n">
-        <v>1077.7</v>
+        <v>1150.8</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>1085.8</v>
+        <v>1159</v>
       </c>
       <c r="D157" t="n">
-        <v>1112</v>
+        <v>1159.3</v>
       </c>
       <c r="E157" t="n">
-        <v>1071.2</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="158">
@@ -3424,16 +3424,16 @@
         </is>
       </c>
       <c r="B158" s="1" t="n">
-        <v>23748.8</v>
+        <v>24241.9</v>
       </c>
       <c r="C158" t="n">
-        <v>23996.7</v>
+        <v>23999.3</v>
       </c>
       <c r="D158" t="n">
-        <v>24065.1</v>
+        <v>24270</v>
       </c>
       <c r="E158" t="n">
-        <v>23711.1</v>
+        <v>24185.4</v>
       </c>
     </row>
     <row r="159">
@@ -3443,16 +3443,16 @@
         </is>
       </c>
       <c r="B159" s="1" t="n">
-        <v>54760</v>
+        <v>58200</v>
       </c>
       <c r="C159" t="n">
-        <v>55207</v>
+        <v>57813</v>
       </c>
       <c r="D159" t="n">
-        <v>55529.4</v>
+        <v>58361.4</v>
       </c>
       <c r="E159" t="n">
-        <v>54601</v>
+        <v>57925</v>
       </c>
     </row>
     <row r="160">
